--- a/tests/fixtures/11_loan_schedule/data-export-control.xlsx
+++ b/tests/fixtures/11_loan_schedule/data-export-control.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -600,231 +600,232 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>amort.payment_no</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>amort.date</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>amort.payment</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>amort.principal</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>amort.interest</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>amort.balance</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="7" t="n">
         <v>46054</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>1702</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>1652</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H7" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I7" s="5" t="n">
         <v>8348</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E8" s="10" t="n">
         <v>46082</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>1702</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G8" s="8" t="n">
         <v>1660.3</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H8" s="8" t="n">
         <v>41.7</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I8" s="8" t="n">
         <v>6687.7</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E9" s="7" t="n">
         <v>46113</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>1702</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>1668.6</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>33.4</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>5019.1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D10" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E10" s="10" t="n">
         <v>46143</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F10" s="8" t="n">
         <v>1702</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G10" s="8" t="n">
         <v>1676.9</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H10" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I10" s="8" t="n">
         <v>3342.2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E11" s="7" t="n">
         <v>46174</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>1702</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>1685.3</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H11" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I11" s="5" t="n">
         <v>1656.9</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D12" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E12" s="10" t="n">
         <v>46204</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F12" s="8" t="n">
         <v>1665.2</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G12" s="8" t="n">
         <v>1656.9</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H12" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I12" s="8" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n">
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n">
         <v>10175.2</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H13" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I13" s="11" t="n">
         <v>175.2</v>
       </c>
     </row>
